--- a/drivers.xlsx
+++ b/drivers.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6895144fd7061132/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Pruthivi\comb\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="8_{FE5C6A9B-F896-4A5D-BE61-FBCDCF8AEA39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8BB0C857-E524-46D7-9D0D-23A4D811739C}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED96ACC6-7040-497E-A2B5-2230DBF5BA0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{14FDBFE2-D83F-4C0D-874F-4051165C5415}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>name</t>
   </si>
@@ -57,19 +57,28 @@
   </si>
   <si>
     <t>phone</t>
+  </si>
+  <si>
+    <t>ramkumar</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF0A2540"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -92,8 +101,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -428,7 +438,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84609FE3-E688-4302-8F2A-6635EB7A1D3F}">
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
@@ -482,6 +492,14 @@
         <v>5</v>
       </c>
     </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" s="1">
+        <v>7358362251</v>
+      </c>
+      <c r="B7" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
